--- a/consent_forms/030_ai_powered_therapy_platform_testing_consent_form--consent_forms.xlsx
+++ b/consent_forms/030_ai_powered_therapy_platform_testing_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -971,29 +971,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_that_this_ai_platform_is_for_research/testing_purposes_only_and_is_not_a_crisis_intervention_or_emergency_medical_service._if_i_am_in_immediate_danger,_i_will_call_emergency_services_(e.g.,_911).',_'value':_'acknowledged'}</t>
+          <t>i_understand_that_this_ai_platform_is_for_research/testing_purposes_only_and_is_not_a_crisis_intervention_or_emergency_medical_service._if_i_am_in_immediate_danger,_i_will_call_emergency_services_(e.g.,_911).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'I understand that this AI platform is for research/testing purposes only and is NOT a crisis intervention or emergency medical service. If I am in immediate danger, I will call emergency services (e.g., 911).', 'value': 'acknowledged'}</t>
+          <t>I understand that this AI platform is for research/testing purposes only and is NOT a crisis intervention or emergency medical service. If I am in immediate danger, I will call emergency services (e.g., 911).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>recording_consent_choices</t>
+          <t>crisis_disclaimer_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_consent_to_recording',_'value':_true}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I consent to recording', 'value': True}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1005,29 +1005,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_do_not_consent_(will_exclude_you_from_the_study)',_'value':_false}</t>
+          <t>yes,_i_consent_to_recording</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'No, I do not consent (Will exclude you from the study)', 'value': False}</t>
+          <t>Yes, I consent to recording</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>training_data_usage_choices</t>
+          <t>recording_consent_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_consent_to_anonymized_training_usage',_'value':_true}</t>
+          <t>no,_i_do_not_consent_(will_exclude_you_from_the_study)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I consent to anonymized training usage', 'value': True}</t>
+          <t>No, I do not consent (Will exclude you from the study)</t>
         </is>
       </c>
     </row>
@@ -1039,97 +1039,148 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'no,_only_use_my_data_for_this_specific_study',_'value':_false}</t>
+          <t>yes,_i_consent_to_anonymized_training_usage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'No, only use my data for this specific study', 'value': False}</t>
+          <t>Yes, I consent to anonymized training usage</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>right_to_withdraw_choices</t>
+          <t>training_data_usage_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand',_'value':_'understood'}</t>
+          <t>no,_only_use_my_data_for_this_specific_study</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'I understand', 'value': 'understood'}</t>
+          <t>No, only use my data for this specific study</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>signature_acknowledgment_choices</t>
+          <t>right_to_withdraw_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_read_this_form_and_voluntarily_agree_to_participate_in_the_platform_testing.',_'value':_'signed'}</t>
+          <t>i_understand</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I have read this form and voluntarily agree to participate in the platform testing.', 'value': 'signed'}</t>
+          <t>I understand</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>testing_hardware_choices</t>
+          <t>right_to_withdraw_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_smartphone_app',_'value':_'mobile_app'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile Smartphone App', 'value': 'mobile_app'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>testing_hardware_choices</t>
+          <t>signature_acknowledgment_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'web_browser_(desktop/laptop)',_'value':_'web_browser'}</t>
+          <t>i_have_read_this_form_and_voluntarily_agree_to_participate_in_the_platform_testing.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Web Browser (Desktop/Laptop)', 'value': 'web_browser'}</t>
+          <t>I have read this form and voluntarily agree to participate in the platform testing.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>signature_acknowledgment_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>testing_hardware_choices</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'label':_'vr_/_ar_headset',_'value':_'vr_headset'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'label': 'VR / AR Headset', 'value': 'vr_headset'}</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mobile_smartphone_app</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mobile Smartphone App</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>testing_hardware_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>web_browser_(desktop/laptop)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Web Browser (Desktop/Laptop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>testing_hardware_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>vr_/_ar_headset</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VR / AR Headset</t>
         </is>
       </c>
     </row>
